--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486286_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486286_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.113099999999999</v>
+        <v>9.728</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6744</v>
+        <v>9.2584</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4388</v>
+        <v>0.4696</v>
       </c>
       <c r="G2" t="n">
         <v>7.0546</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0155</v>
+        <v>1.6304</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9542</v>
+        <v>1.5382</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0614</v>
+        <v>0.0922</v>
       </c>
       <c r="V2" t="n">
         <v>0.3904</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7795</v>
+        <v>2.6333</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5067</v>
+        <v>2.9031</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2728</v>
+        <v>-0.2698</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6868</v>
+        <v>0.6312</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4591</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1459</v>
+        <v>-0.2996</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5921</v>
+        <v>2.7805</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5538</v>
+        <v>1.9773</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0382</v>
+        <v>0.8032</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09470000000000001</v>
+        <v>-2.1493</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0129</v>
+        <v>-1.0464</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1076</v>
+        <v>-1.1029</v>
       </c>
       <c r="P3" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.435</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0073</v>
+        <v>0.131</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6992</v>
+        <v>0.5576</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3081</v>
+        <v>-0.4266</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5204</v>
+        <v>1.6536</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.6536</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8375</v>
+        <v>2.5887</v>
       </c>
       <c r="E4" t="n">
-        <v>1.053</v>
+        <v>1.5008</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7845</v>
+        <v>1.0879</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6947</v>
+        <v>0.6868</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4174</v>
+        <v>-0.4591</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7228</v>
+        <v>1.1459</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9061</v>
+        <v>0.5921</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1378</v>
+        <v>0.5538</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.0439</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6008</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2796</v>
+        <v>-1.0129</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3212</v>
+        <v>1.1076</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6934</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.5204</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5204</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.5225</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.7503</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.8292</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.9211</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.2599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3961</v>
+        <v>2.2244</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5426</v>
+        <v>2.338</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1465</v>
+        <v>-0.1136</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6312</v>
+        <v>2.1326</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9308999999999999</v>
+        <v>-0.2069</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2996</v>
+        <v>2.3396</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7805</v>
+        <v>2.022</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9773</v>
+        <v>0.1095</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8032</v>
+        <v>1.9125</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1493</v>
+        <v>0.1107</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0464</v>
+        <v>-0.3164</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1029</v>
+        <v>0.4271</v>
       </c>
       <c r="P5" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1062</v>
+        <v>0.4392</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1971</v>
+        <v>0.5336</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3033</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6536</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.6536</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3552</v>
+        <v>2.1769</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5305</v>
+        <v>0.8548</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1753</v>
+        <v>1.3221</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1326</v>
+        <v>0.6947</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2069</v>
+        <v>1.4174</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3396</v>
+        <v>-0.7228</v>
       </c>
       <c r="J6" t="n">
-        <v>2.022</v>
+        <v>-0.9061</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1095</v>
+        <v>1.1378</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9125</v>
+        <v>-2.0439</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1107</v>
+        <v>1.6008</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3164</v>
+        <v>0.2796</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4271</v>
+        <v>1.3212</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.43</v>
+        <v>1.0896</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>0.6309</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.156</v>
+        <v>0.4587</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8615</v>
+        <v>0.8522</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0267</v>
+        <v>0.3955</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1652</v>
+        <v>0.4567</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2112</v>
+        <v>-0.3308</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8496</v>
+        <v>0.517</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6384</v>
+        <v>-0.8478</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4175</v>
+        <v>0.0104</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.7977</v>
+        <v>1.1164</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3802</v>
+        <v>-1.106</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2063</v>
+        <v>-0.3412</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0519</v>
+        <v>-0.5994</v>
       </c>
       <c r="O7" t="n">
         <v>0.2582</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5502</v>
+        <v>-0.0997</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6618</v>
+        <v>0.1899</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1115</v>
+        <v>-0.2896</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5119</v>
+        <v>0.5291</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3017</v>
+        <v>1.5347</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2101</v>
+        <v>-1.0055</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3308</v>
+        <v>0.169</v>
       </c>
       <c r="H8" t="n">
-        <v>0.517</v>
+        <v>0.9579</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8478</v>
+        <v>-0.7889</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0104</v>
+        <v>1.7086</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1164</v>
+        <v>1.0767</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.106</v>
+        <v>0.6319</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3412</v>
+        <v>-1.5397</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5994</v>
+        <v>-0.1188</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2582</v>
+        <v>-1.4208</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4401</v>
+        <v>0.3395</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0961</v>
+        <v>1.1104</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5362</v>
+        <v>-0.7709</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0.0207</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0.0207</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5434</v>
+        <v>0.2779</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7704</v>
+        <v>0.3814</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3138</v>
+        <v>-0.1036</v>
       </c>
       <c r="G9" t="n">
-        <v>0.169</v>
+        <v>-1.2112</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9579</v>
+        <v>-2.8496</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7889</v>
+        <v>1.6384</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7086</v>
+        <v>-1.4175</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0767</v>
+        <v>-2.7977</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6319</v>
+        <v>1.3802</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5397</v>
+        <v>0.2063</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1188</v>
+        <v>-0.0519</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4208</v>
+        <v>0.2582</v>
       </c>
       <c r="P9" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.9666</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.0165</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.305</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.305</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.733</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.3461</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-1.0791</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.0207</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.0207</v>
-      </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9431</v>
+        <v>-0.8506</v>
       </c>
       <c r="E10" t="n">
         <v>-1.1378</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1947</v>
+        <v>0.2872</v>
       </c>
       <c r="G10" t="n">
         <v>-0.06619999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0068</v>
+        <v>0.0856</v>
       </c>
       <c r="T10" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2234</v>
+        <v>-2.6587</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8457</v>
+        <v>-2.3734</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3777</v>
+        <v>-0.2852</v>
       </c>
       <c r="G11" t="n">
         <v>0.3745</v>
@@ -1312,13 +1312,13 @@
         <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.4894</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0277</v>
+        <v>0.4999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.103</v>
+        <v>-0.0105</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3043</v>
+        <v>-3.2906</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7524</v>
+        <v>-2.6154</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.6752</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5804</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0805</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1899</v>
+        <v>-0.0529</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0956</v>
+        <v>-0.0277</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0647</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.8406</v>
+        <v>14.2106</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6701</v>
+        <v>13.0401</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1705</v>
+        <v>1.1706</v>
       </c>
       <c r="G13" t="n">
-        <v>8.5548</v>
+        <v>8.554799999999997</v>
       </c>
       <c r="H13" t="n">
         <v>1.0045</v>
       </c>
       <c r="I13" t="n">
-        <v>7.550299999999998</v>
+        <v>7.550299999999999</v>
       </c>
       <c r="J13" t="n">
         <v>12.0544</v>
@@ -1447,7 +1447,7 @@
         <v>5.918200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>6.135999999999999</v>
+        <v>6.136000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-3.4995</v>
@@ -1468,13 +1468,13 @@
         <v>11.9627</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4377</v>
+        <v>6.807700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>6.279000000000001</v>
+        <v>7.649</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8412999999999999</v>
+        <v>-0.8412999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2394</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3157</v>
+        <v>1.6982</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8236</v>
+        <v>3.5954</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5079</v>
+        <v>-1.8972</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2663</v>
+        <v>0.0464</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3314</v>
+        <v>0.0727</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5977</v>
+        <v>-0.0263</v>
       </c>
       <c r="J14" t="n">
-        <v>0.969</v>
+        <v>1.7176</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9307</v>
+        <v>0.1095</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0382</v>
+        <v>1.6081</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2353</v>
+        <v>-1.6712</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5994</v>
+        <v>-0.0368</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6359</v>
+        <v>-1.6344</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R14" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06</v>
+        <v>-0.718</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9421</v>
+        <v>-0.1646</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8822</v>
+        <v>-0.5534</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3045</v>
+        <v>1.4997</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1745</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8542</v>
+        <v>0.8751</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8131</v>
+        <v>2.2648</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9589</v>
+        <v>-1.3897</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0464</v>
+        <v>-0.2663</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0727</v>
+        <v>0.3314</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0263</v>
+        <v>-0.5977</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7176</v>
+        <v>0.969</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1095</v>
+        <v>0.9307</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6081</v>
+        <v>0.0382</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6712</v>
+        <v>-1.2353</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0368</v>
+        <v>-0.5994</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6344</v>
+        <v>-0.6359</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.562</v>
+        <v>-0.3806</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9469</v>
+        <v>0.3833</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.615</v>
+        <v>-0.764</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4997</v>
+        <v>1.3045</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7602</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2521</v>
+        <v>0.3665</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0609</v>
+        <v>0.2883</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8088</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1657</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3443</v>
+        <v>-1.4203</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1785</v>
+        <v>0.4773</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8752</v>
+        <v>-0.0057</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9955</v>
+        <v>-0.5229</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8797</v>
+        <v>0.5172</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7095</v>
+        <v>-0.9372</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6512</v>
+        <v>-0.8974</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0583</v>
+        <v>-0.0399</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.5225</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5655</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6223</v>
+        <v>-0.4434</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0569</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.044</v>
+        <v>2.0647</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.9141</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>M. FRIERSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1086</v>
+        <v>0.1055</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3</v>
+        <v>1.8428</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4086</v>
+        <v>-1.7374</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2545</v>
+        <v>-0.4737</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4506</v>
+        <v>-0.806</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1961</v>
+        <v>0.3323</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8937</v>
+        <v>0.548</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7519</v>
+        <v>-0.5046</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8582</v>
+        <v>1.0527</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6392</v>
+        <v>-1.0217</v>
       </c>
       <c r="N17" t="n">
         <v>-0.3013</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3379</v>
+        <v>-0.7204</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-0.435</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4419</v>
+        <v>-0.6606</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0036</v>
+        <v>0.0349</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4382</v>
+        <v>-0.6955</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9347</v>
+        <v>0.3698</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7395</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2193</v>
+        <v>0.0161</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1588</v>
+        <v>-1.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0606</v>
+        <v>1.3161</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9429999999999999</v>
+        <v>0.2545</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4203</v>
+        <v>1.4506</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4773</v>
+        <v>-1.1961</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0057</v>
+        <v>0.8937</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5229</v>
+        <v>1.7519</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5172</v>
+        <v>-0.8582</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9372</v>
+        <v>-0.6392</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8974</v>
+        <v>-0.3013</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0399</v>
+        <v>-0.3379</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5225</v>
+        <v>-2.3926</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1236</v>
+        <v>0.3494</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8904</v>
+        <v>0.0036</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2331</v>
+        <v>0.3458</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0647</v>
+        <v>0.9347</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FRIERSON</t>
+          <t>T. HOLLOWELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3711</v>
+        <v>-0.0599</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7311</v>
+        <v>0.8406</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1021</v>
+        <v>-0.9004</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4737</v>
+        <v>-1.4849</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.806</v>
+        <v>-1.4236</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3323</v>
+        <v>-0.0613</v>
       </c>
       <c r="J19" t="n">
-        <v>0.548</v>
+        <v>0.5027</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5046</v>
+        <v>-0.3253</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0527</v>
+        <v>0.828</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0217</v>
+        <v>-1.9876</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3013</v>
+        <v>-1.0983</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7204</v>
+        <v>-0.8893</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="R19" t="n">
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1372</v>
+        <v>-0.5972</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0769</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0603</v>
+        <v>-0.5876</v>
       </c>
       <c r="V19" t="n">
+        <v>0.9347</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="X19" t="n">
         <v>0.3698</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2121</v>
+        <v>-0.5481</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4918</v>
+        <v>1.0551</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-1.6033</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4678</v>
+        <v>1.1657</v>
       </c>
       <c r="H20" t="n">
-        <v>0.216</v>
+        <v>1.3443</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2518</v>
+        <v>-0.1785</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7531</v>
+        <v>2.8752</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7149</v>
+        <v>1.9955</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>0.8797</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2854</v>
+        <v>-1.7095</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4989</v>
+        <v>-0.6512</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2136</v>
+        <v>-1.0583</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3926</v>
+        <v>-1.5225</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3854</v>
+        <v>0.7652</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1476</v>
+        <v>0.6165</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7622</v>
+        <v>0.1487</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7602</v>
+        <v>-2.044</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.9141</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. HOLLOWELL</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7336</v>
+        <v>-2.0496</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1652</v>
+        <v>-1.3859</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5683</v>
+        <v>-0.6637</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4849</v>
+        <v>0.4678</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4236</v>
+        <v>0.216</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0613</v>
+        <v>0.2518</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5027</v>
+        <v>0.7531</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3253</v>
+        <v>0.7149</v>
       </c>
       <c r="L21" t="n">
-        <v>0.828</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9876</v>
+        <v>-0.2854</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0983</v>
+        <v>-0.4989</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8893</v>
+        <v>0.2136</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.3926</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.0875</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-0.2175</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.305</v>
-      </c>
       <c r="S21" t="n">
-        <v>-2.271</v>
+        <v>-0.4521</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0154</v>
+        <v>0.2536</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2555</v>
+        <v>-0.7057</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9347</v>
+        <v>-0.7602</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3698</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>I. MASSOUD RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3917</v>
+        <v>-2.6974</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8548</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5369</v>
+        <v>-1.9518</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2876</v>
+        <v>-1.2463</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9823</v>
+        <v>0.447</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3053</v>
+        <v>-1.6933</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.03</v>
+        <v>-0.0906</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.465</v>
+        <v>1.6274</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.565</v>
+        <v>-1.718</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2576</v>
+        <v>-1.1556</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5173</v>
+        <v>-1.1803</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7403</v>
+        <v>0.0247</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="R22" t="n">
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.853</v>
+        <v>-0.7784</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2197</v>
+        <v>-0.2199</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3668</v>
+        <v>-0.5585</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7395</v>
+        <v>-1.3252</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. MASSOUD RODRÍGUEZ</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0307</v>
+        <v>-4.0494</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4161</v>
+        <v>-3.7489</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6146</v>
+        <v>-0.3005</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2463</v>
+        <v>-3.2876</v>
       </c>
       <c r="H23" t="n">
-        <v>0.447</v>
+        <v>-0.9823</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6933</v>
+        <v>-2.3053</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0906</v>
+        <v>-2.03</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6274</v>
+        <v>-0.465</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.718</v>
+        <v>-1.565</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1556</v>
+        <v>-1.2576</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1803</v>
+        <v>-0.5173</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0247</v>
+        <v>-0.7403</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="R23" t="n">
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1117</v>
+        <v>0.1953</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>0.3257</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2213</v>
+        <v>-0.1304</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3252</v>
+        <v>-0.7395</v>
       </c>
       <c r="W23" t="n">
+        <v>-0.7395</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4128</v>
+        <v>-4.2624</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2125</v>
+        <v>-3.8772</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2003</v>
+        <v>-0.3852</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7873</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5379</v>
+        <v>-0.3876</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.274</v>
+        <v>0.0613</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2639</v>
+        <v>-0.4488</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.8407</v>
+        <v>-10.6054</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.170500000000001</v>
+        <v>-1.1705</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.6701</v>
+        <v>-9.434899999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-8.5547</v>
@@ -2380,7 +2380,7 @@
         <v>3.499500000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.913799999999999</v>
+        <v>4.9138</v>
       </c>
       <c r="L25" t="n">
         <v>-1.414299999999999</v>
@@ -2392,7 +2392,7 @@
         <v>-5.9181</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.1361</v>
+        <v>-6.136099999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-1.0875</v>
@@ -2404,13 +2404,13 @@
         <v>10.875</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.4376</v>
+        <v>-3.202399999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8412999999999999</v>
+        <v>0.8414</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.279</v>
+        <v>-4.0437</v>
       </c>
       <c r="V25" t="n">
         <v>2.2392</v>
@@ -2419,7 +2419,7 @@
         <v>6.4514</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.2122</v>
+        <v>-4.212199999999999</v>
       </c>
     </row>
   </sheetData>
